--- a/data/mapas/Mapa_de_Carrera_Informatica.xlsx
+++ b/data/mapas/Mapa_de_Carrera_Informatica.xlsx
@@ -555,13 +555,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="J3" s="5">
-        <f>COUNTIF(B6:B61, "SI")</f>
+        <f>COUNTIF(B6:B42, "SI")</f>
         <v/>
       </c>
     </row>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="J4" s="5">
-        <f>COUNTIF(C6:C61, "SI")</f>
+        <f>COUNTIF(C6:C42, "SI")</f>
         <v/>
       </c>
     </row>
@@ -667,14 +667,14 @@
         </is>
       </c>
       <c r="J5" s="5">
-        <f>COUNTIF(F6:F61, "ADEUDA FINAL")</f>
+        <f>COUNTIF(F6:F42, "ADEUDA FINAL")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Álgebra I</t>
+          <t>Algoritmos y Estructuras de Datos I</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -710,14 +710,14 @@
         </is>
       </c>
       <c r="J6" s="12">
-        <f>COUNTIF(B6:B61, "SI")/50</f>
+        <f>COUNTIF(B6:B42, "SI")/33</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Diseño I</t>
+          <t>Arquitectura y Organización de Computadoras</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -753,14 +753,14 @@
         </is>
       </c>
       <c r="J7" s="12">
-        <f>COUNTIF(C6:C61, "SI")/50</f>
+        <f>COUNTIF(C6:C42, "SI")/33</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Herramientas Informaticas</t>
+          <t>Fundamentos de Informática y Sistemas Digitales</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Informática</t>
+          <t>Matemática Discreta y Álgebra Lineal</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
+          <t>Pedagogía</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -872,7 +872,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Pedagogía</t>
+          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -911,7 +911,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Programacion I</t>
+          <t>Trabajo de Campo I</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -948,37 +948,10 @@
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Psicología EDUCACIONAL</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>1° Año</t>
-        </is>
-      </c>
-      <c r="E13" s="10">
-        <f>IF(B13="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F13" s="10">
-        <f>IF(C13="SI", "APROBADO", IF(B13="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G13" s="11">
-        <f>IF(C13="SI", "🟢 Aprobada", IF(B13="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>📌 2° AÑO</t>
+        </is>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -989,7 +962,7 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Sujetos de Nivel</t>
+          <t>Algoritmos y Estructuras de Datos II</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -1004,7 +977,7 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>1° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E14" s="10">
@@ -1028,7 +1001,7 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Trabajo de Campo I</t>
+          <t>Sistemas Operativos y Redes de Comunicación</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -1043,7 +1016,7 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>1° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E15" s="10">
@@ -1064,17 +1037,44 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>📌 2° AÑO</t>
-        </is>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Bases de Datos I</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E16" s="10">
+        <f>IF(B16="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F16" s="10">
+        <f>IF(C16="SI", "APROBADO", IF(B16="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G16" s="11">
+        <f>IF(C16="SI", "🟢 Aprobada", IF(B16="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>CALCULO PARA Informática</t>
+          <t>Programación Orientada a Objetos</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -1108,7 +1108,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Didáctica GENERAL</t>
+          <t>Didáctica General</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -1142,7 +1142,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Diseño II (taller)</t>
+          <t>Psicología Educacional</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -1176,7 +1176,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Educación SEXUAL INTEGRAL</t>
+          <t>Sujetos de la Educación</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -1210,7 +1210,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Programacion II</t>
+          <t>Trabajo de Campo II</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -1241,44 +1241,17 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>Sistemas Informaticos</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>2° Año</t>
-        </is>
-      </c>
-      <c r="E22" s="10">
-        <f>IF(B22="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F22" s="10">
-        <f>IF(C22="SI", "APROBADO", IF(B22="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G22" s="11">
-        <f>IF(C22="SI", "🟢 Aprobada", IF(B22="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>📌 3° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Tecnologia de la Informacion y la Comun</t>
+          <t>Ingeniería de Software y Desarrollo Web</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -1293,7 +1266,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E23" s="10">
@@ -1312,7 +1285,7 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Trabajo de Campo II</t>
+          <t>Bases de Datos II y Administración de Servidores</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -1327,7 +1300,7 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E24" s="10">
@@ -1343,17 +1316,44 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>📌 3° AÑO</t>
-        </is>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Informática Educativa I y Entornos Virtuales</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E25" s="10">
+        <f>IF(B25="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F25" s="10">
+        <f>IF(C25="SI", "APROBADO", IF(B25="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G25" s="11">
+        <f>IF(C25="SI", "🟢 Aprobada", IF(B25="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Derecho Humanos, Sociedad y Estado</t>
+          <t>Didáctica de la Informática I</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1387,7 +1387,7 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Discursos Digitales</t>
+          <t>Seguridad Informática y Ética Digital</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Filosofía</t>
+          <t>Historia Social de la Educación</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1455,7 +1455,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Informática Educativa I</t>
+          <t>Derechos Humanos, Sociedad y Estado</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -1489,7 +1489,7 @@
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>Inglés I</t>
+          <t>Construcción de la Práctica Docente I</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
@@ -1520,44 +1520,17 @@
         <v/>
       </c>
     </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>LOGICA Informática</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>3° Año</t>
-        </is>
-      </c>
-      <c r="E31" s="10">
-        <f>IF(B31="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F31" s="10">
-        <f>IF(C31="SI", "APROBADO", IF(B31="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G31" s="11">
-        <f>IF(C31="SI", "🟢 Aprobada", IF(B31="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>📌 4° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Programacion III</t>
+          <t>Tecnologías Emergentes, IA y Ciencia de Datos</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -1572,7 +1545,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E32" s="10">
@@ -1591,7 +1564,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Redes y Comunicación de Datos</t>
+          <t>Informática Educativa II y Robótica Pedagógica</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -1606,7 +1579,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E33" s="10">
@@ -1622,17 +1595,44 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>📌 4° AÑO</t>
-        </is>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Discursos y Culturas Digitales</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E34" s="10">
+        <f>IF(B34="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F34" s="10">
+        <f>IF(C34="SI", "APROBADO", IF(B34="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G34" s="11">
+        <f>IF(C34="SI", "🟢 Aprobada", IF(B34="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>Const. de la Pract. Docente I</t>
+          <t>Didáctica de la Informática II</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>HISTORIA DE LA Educación ARGENTINA</t>
+          <t>Educación Sexual Integral (ESI)</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -1700,7 +1700,7 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>Informática Educativa II</t>
+          <t>Ética y Trabajo Docente</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -1734,7 +1734,7 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>Inglés II</t>
+          <t>Residencia y Construcción de la Práctica Docente II</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
@@ -1765,44 +1765,17 @@
         <v/>
       </c>
     </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>Nuevos Escenarios Cultura Tecnol y Sub</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D39" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E39" s="10">
-        <f>IF(B39="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F39" s="10">
-        <f>IF(C39="SI", "APROBADO", IF(B39="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G39" s="11">
-        <f>IF(C39="SI", "🟢 Aprobada", IF(B39="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
+        </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Proyectos Educativos</t>
+          <t>Seminario de Redes Avanzadas y Cloud Computing</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -1817,7 +1790,7 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E40" s="10">
@@ -1836,7 +1809,7 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>Recursos Inform. Aplic.a Otras Discip</t>
+          <t>Seminario de Accesibilidad y Tecnologías Inclusivas</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -1851,7 +1824,7 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E41" s="10">
@@ -1870,7 +1843,7 @@
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>Recursos Informaticos</t>
+          <t>Taller de Proyecto Final de Informática</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
@@ -1885,7 +1858,7 @@
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E42" s="10">
@@ -1901,593 +1874,26 @@
         <v/>
       </c>
     </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>Tecnicas Digitales</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E43" s="10">
-        <f>IF(B43="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F43" s="10">
-        <f>IF(C43="SI", "APROBADO", IF(B43="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G43" s="11">
-        <f>IF(C43="SI", "🟢 Aprobada", IF(B43="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>📌 5° AÑO (NIVEL SUPERIOR / TRAMO SUPERIOR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>Construcción de la Práctica DocenteII Y RESID. N. SUPERIOR</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D45" s="10" t="inlineStr">
-        <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E45" s="10">
-        <f>IF(B45="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F45" s="10">
-        <f>IF(C45="SI", "APROBADO", IF(B45="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G45" s="11">
-        <f>IF(C45="SI", "🟢 Aprobada", IF(B45="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>Diseño de Sistemas (seminario)</t>
-        </is>
-      </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D46" s="10" t="inlineStr">
-        <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E46" s="10">
-        <f>IF(B46="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F46" s="10">
-        <f>IF(C46="SI", "APROBADO", IF(B46="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G46" s="11">
-        <f>IF(C46="SI", "🟢 Aprobada", IF(B46="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>Inteligencia Artificial</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D47" s="10" t="inlineStr">
-        <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E47" s="10">
-        <f>IF(B47="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F47" s="10">
-        <f>IF(C47="SI", "APROBADO", IF(B47="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G47" s="11">
-        <f>IF(C47="SI", "🟢 Aprobada", IF(B47="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t>LENGUA EXTRANJERA PORTUGUES (Cuatrim)</t>
-        </is>
-      </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C48" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D48" s="10" t="inlineStr">
-        <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E48" s="10">
-        <f>IF(B48="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F48" s="10">
-        <f>IF(C48="SI", "APROBADO", IF(B48="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G48" s="11">
-        <f>IF(C48="SI", "🟢 Aprobada", IF(B48="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t>SISTEMA Y Política Educativa (1° CUATRIM.)</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C49" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D49" s="10" t="inlineStr">
-        <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E49" s="10">
-        <f>IF(B49="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F49" s="10">
-        <f>IF(C49="SI", "APROBADO", IF(B49="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G49" s="11">
-        <f>IF(C49="SI", "🟢 Aprobada", IF(B49="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="8" t="inlineStr">
-        <is>
-          <t>Modelización Matemática y Simulación</t>
-        </is>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C50" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D50" s="10" t="inlineStr">
-        <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E50" s="10">
-        <f>IF(B50="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F50" s="10">
-        <f>IF(C50="SI", "APROBADO", IF(B50="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G50" s="11">
-        <f>IF(C50="SI", "🟢 Aprobada", IF(B50="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>📌 6° AÑO (NIVEL SUPERIOR / TRAMO SUPERIOR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>Seminario de Especialización Superior II</t>
-        </is>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D52" s="10" t="inlineStr">
-        <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E52" s="10">
-        <f>IF(B52="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F52" s="10">
-        <f>IF(C52="SI", "APROBADO", IF(B52="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G52" s="11">
-        <f>IF(C52="SI", "🟢 Aprobada", IF(B52="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>Tesis / Trabajo Final de Licenciatura</t>
-        </is>
-      </c>
-      <c r="B53" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C53" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D53" s="10" t="inlineStr">
-        <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E53" s="10">
-        <f>IF(B53="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F53" s="10">
-        <f>IF(C53="SI", "APROBADO", IF(B53="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G53" s="11">
-        <f>IF(C53="SI", "🟢 Aprobada", IF(B53="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>Práctica de Nivel Superior II</t>
-        </is>
-      </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C54" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D54" s="10" t="inlineStr">
-        <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E54" s="10">
-        <f>IF(B54="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F54" s="10">
-        <f>IF(C54="SI", "APROBADO", IF(B54="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G54" s="11">
-        <f>IF(C54="SI", "🟢 Aprobada", IF(B54="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>Acreditación de Residencia Superior</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C55" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D55" s="10" t="inlineStr">
-        <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E55" s="10">
-        <f>IF(B55="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F55" s="10">
-        <f>IF(C55="SI", "APROBADO", IF(B55="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G55" s="11">
-        <f>IF(C55="SI", "🟢 Aprobada", IF(B55="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>📌 GENERAL / OPTATIVAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>Álgebra</t>
-        </is>
-      </c>
-      <c r="B57" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C57" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D57" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E57" s="10">
-        <f>IF(B57="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F57" s="10">
-        <f>IF(C57="SI", "APROBADO", IF(B57="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G57" s="11">
-        <f>IF(C57="SI", "🟢 Aprobada", IF(B57="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="8" t="inlineStr">
-        <is>
-          <t>Derechos Humanos SOCIEDAD Y ESTADO</t>
-        </is>
-      </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C58" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D58" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E58" s="10">
-        <f>IF(B58="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F58" s="10">
-        <f>IF(C58="SI", "APROBADO", IF(B58="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G58" s="11">
-        <f>IF(C58="SI", "🟢 Aprobada", IF(B58="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="8" t="inlineStr">
-        <is>
-          <t>Diseño de Sistemas</t>
-        </is>
-      </c>
-      <c r="B59" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C59" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D59" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E59" s="10">
-        <f>IF(B59="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F59" s="10">
-        <f>IF(C59="SI", "APROBADO", IF(B59="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G59" s="11">
-        <f>IF(C59="SI", "🟢 Aprobada", IF(B59="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="8" t="inlineStr">
-        <is>
-          <t>Diseño II</t>
-        </is>
-      </c>
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C60" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D60" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E60" s="10">
-        <f>IF(B60="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F60" s="10">
-        <f>IF(C60="SI", "APROBADO", IF(B60="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G60" s="11">
-        <f>IF(C60="SI", "🟢 Aprobada", IF(B60="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="8" t="inlineStr">
-        <is>
-          <t>Nuevos Escenarios, Culturas Tecnolog</t>
-        </is>
-      </c>
-      <c r="B61" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C61" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D61" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E61" s="10">
-        <f>IF(B61="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F61" s="10">
-        <f>IF(C61="SI", "APROBADO", IF(B61="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G61" s="11">
-        <f>IF(C61="SI", "🟢 Aprobada", IF(B61="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="A44:G44"/>
+  <mergeCells count="15">
+    <mergeCell ref="A13:G13"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="A31:G31"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="I10:J10"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A39:G39"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="I14:J14"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B17 B18 B19 B20 B21 B22 B23 B24 B26 B27 B28 B29 B30 B31 B32 B33 B35 B36 B37 B38 B39 B40 B41 B42 B43 B45 B46 B47 B48 B49 B50 B52 B53 B54 B55 B57 B58 B59 B60 B61 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C17 C18 C19 C20 C21 C22 C23 C24 C26 C27 C28 C29 C30 C31 C32 C33 C35 C36 C37 C38 C39 C40 C41 C42 C43 C45 C46 C47 C48 C49 C50 C52 C53 C54 C55 C57 C58 C59 C60 C61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B14 B15 B16 B17 B18 B19 B20 B21 B23 B24 B25 B26 B27 B28 B29 B30 B32 B33 B34 B35 B36 B37 B38 B40 B41 B42 C6 C7 C8 C9 C10 C11 C12 C14 C15 C16 C17 C18 C19 C20 C21 C23 C24 C25 C26 C27 C28 C29 C30 C32 C33 C34 C35 C36 C37 C38 C40 C41 C42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/mapas/Mapa_de_Carrera_Informatica.xlsx
+++ b/data/mapas/Mapa_de_Carrera_Informatica.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="J3" s="5">
-        <f>COUNTIF(B6:B42, "SI")</f>
+        <f>COUNTIF(B6:B49, "SI")</f>
         <v/>
       </c>
     </row>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="J4" s="5">
-        <f>COUNTIF(C6:C42, "SI")</f>
+        <f>COUNTIF(C6:C49, "SI")</f>
         <v/>
       </c>
     </row>
@@ -667,14 +667,14 @@
         </is>
       </c>
       <c r="J5" s="5">
-        <f>COUNTIF(F6:F42, "ADEUDA FINAL")</f>
+        <f>COUNTIF(F6:F49, "ADEUDA FINAL")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Algoritmos y Estructuras de Datos I</t>
+          <t>Álgebra</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -710,14 +710,14 @@
         </is>
       </c>
       <c r="J6" s="12">
-        <f>COUNTIF(B6:B42, "SI")/33</f>
+        <f>COUNTIF(B6:B49, "SI")/40</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Arquitectura y Organización de Computadoras</t>
+          <t>Herramientas informaticas</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -753,14 +753,14 @@
         </is>
       </c>
       <c r="J7" s="12">
-        <f>COUNTIF(C6:C42, "SI")/33</f>
+        <f>COUNTIF(C6:C49, "SI")/40</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Fundamentos de Informática y Sistemas Digitales</t>
+          <t>Trabajo de Campo I</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Matemática Discreta y Álgebra Lineal</t>
+          <t>Programación 1</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Pedagogía</t>
+          <t>Diseño 1</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -872,7 +872,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
+          <t>Informatica</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -911,7 +911,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Trabajo de Campo I</t>
+          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -948,10 +948,37 @@
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>📌 2° AÑO</t>
-        </is>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Psicología Educacional</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>1° Año</t>
+        </is>
+      </c>
+      <c r="E13" s="10">
+        <f>IF(B13="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F13" s="10">
+        <f>IF(C13="SI", "APROBADO", IF(B13="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G13" s="11">
+        <f>IF(C13="SI", "🟢 Aprobada", IF(B13="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -962,7 +989,7 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Algoritmos y Estructuras de Datos II</t>
+          <t>Sujetos de nivel</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -977,7 +1004,7 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E14" s="10">
@@ -1001,7 +1028,7 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Sistemas Operativos y Redes de Comunicación</t>
+          <t>Pedagogía</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -1016,7 +1043,7 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E15" s="10">
@@ -1037,44 +1064,17 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Bases de Datos I</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>2° Año</t>
-        </is>
-      </c>
-      <c r="E16" s="10">
-        <f>IF(B16="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F16" s="10">
-        <f>IF(C16="SI", "APROBADO", IF(B16="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G16" s="11">
-        <f>IF(C16="SI", "🟢 Aprobada", IF(B16="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>📌 2° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Programación Orientada a Objetos</t>
+          <t>Calculo para informatica</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -1108,7 +1108,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Didáctica General</t>
+          <t>Tecnologia de la información y la comunicación</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -1142,7 +1142,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Psicología Educacional</t>
+          <t>Trabajo de Campo II</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -1176,7 +1176,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Sujetos de la Educación</t>
+          <t>Sistemas informaticos</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -1210,7 +1210,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Trabajo de Campo II</t>
+          <t>Lectura, Escritura y Oralidad II (LEO 2)</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -1241,17 +1241,44 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>📌 3° AÑO</t>
-        </is>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Diseño 2</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E22" s="10">
+        <f>IF(B22="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F22" s="10">
+        <f>IF(C22="SI", "APROBADO", IF(B22="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G22" s="11">
+        <f>IF(C22="SI", "🟢 Aprobada", IF(B22="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Ingeniería de Software y Desarrollo Web</t>
+          <t>Programación 2</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -1266,7 +1293,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E23" s="10">
@@ -1285,7 +1312,7 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Bases de Datos II y Administración de Servidores</t>
+          <t>Didáctica general</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -1300,7 +1327,7 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E24" s="10">
@@ -1319,7 +1346,7 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Informática Educativa I y Entornos Virtuales</t>
+          <t>Esi</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -1334,7 +1361,7 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E25" s="10">
@@ -1350,44 +1377,17 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>Didáctica de la Informática I</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>3° Año</t>
-        </is>
-      </c>
-      <c r="E26" s="10">
-        <f>IF(B26="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F26" s="10">
-        <f>IF(C26="SI", "APROBADO", IF(B26="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G26" s="11">
-        <f>IF(C26="SI", "🟢 Aprobada", IF(B26="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>📌 3° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Seguridad Informática y Ética Digital</t>
+          <t>Informatica educativa</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Historia Social de la Educación</t>
+          <t>Filosofía</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1455,7 +1455,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Derechos Humanos, Sociedad y Estado</t>
+          <t>Ingles 1</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -1489,7 +1489,7 @@
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>Construcción de la Práctica Docente I</t>
+          <t>Redes y comunicaciones de datos</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
@@ -1520,17 +1520,44 @@
         <v/>
       </c>
     </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>📌 4° AÑO</t>
-        </is>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Discursos digitales</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E31" s="10">
+        <f>IF(B31="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F31" s="10">
+        <f>IF(C31="SI", "APROBADO", IF(B31="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G31" s="11">
+        <f>IF(C31="SI", "🟢 Aprobada", IF(B31="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Tecnologías Emergentes, IA y Ciencia de Datos</t>
+          <t>Logica informatica</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -1545,7 +1572,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E32" s="10">
@@ -1564,7 +1591,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Informática Educativa II y Robótica Pedagógica</t>
+          <t>Programación 3</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -1579,7 +1606,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E33" s="10">
@@ -1598,7 +1625,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>Discursos y Culturas Digitales</t>
+          <t>DDHH, sociedad y estado</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -1613,7 +1640,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E34" s="10">
@@ -1629,44 +1656,17 @@
         <v/>
       </c>
     </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>Didáctica de la Informática II</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E35" s="10">
-        <f>IF(B35="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F35" s="10">
-        <f>IF(C35="SI", "APROBADO", IF(B35="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G35" s="11">
-        <f>IF(C35="SI", "🟢 Aprobada", IF(B35="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>📌 4° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>Educación Sexual Integral (ESI)</t>
+          <t>Recursos informaticos aplicados a otras disciplinas</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -1700,7 +1700,7 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>Ética y Trabajo Docente</t>
+          <t>Proyectos educativos</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -1734,7 +1734,7 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>Residencia y Construcción de la Práctica Docente II</t>
+          <t>Construcción de la practica docente 1</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
@@ -1765,17 +1765,44 @@
         <v/>
       </c>
     </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
-        </is>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Historia de la educación Argentina</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E39" s="10">
+        <f>IF(B39="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F39" s="10">
+        <f>IF(C39="SI", "APROBADO", IF(B39="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G39" s="11">
+        <f>IF(C39="SI", "🟢 Aprobada", IF(B39="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Redes Avanzadas y Cloud Computing</t>
+          <t>Nuevos escenarios, cultura tecnologica y subjetividad</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -1790,7 +1817,7 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E40" s="10">
@@ -1809,7 +1836,7 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Accesibilidad y Tecnologías Inclusivas</t>
+          <t>Ingles 2</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -1824,7 +1851,7 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E41" s="10">
@@ -1843,7 +1870,7 @@
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>Taller de Proyecto Final de Informática</t>
+          <t>Informatica educativa 2</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
@@ -1858,7 +1885,7 @@
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E42" s="10">
@@ -1874,18 +1901,229 @@
         <v/>
       </c>
     </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>Tecnicas digitales</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E43" s="10">
+        <f>IF(B43="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F43" s="10">
+        <f>IF(C43="SI", "APROBADO", IF(B43="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G43" s="11">
+        <f>IF(C43="SI", "🟢 Aprobada", IF(B43="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>📌 5° AÑO</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>Diseño de sistemas</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E45" s="10">
+        <f>IF(B45="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F45" s="10">
+        <f>IF(C45="SI", "APROBADO", IF(B45="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G45" s="11">
+        <f>IF(C45="SI", "🟢 Aprobada", IF(B45="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>Modelizacion matemática y simulación</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E46" s="10">
+        <f>IF(B46="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F46" s="10">
+        <f>IF(C46="SI", "APROBADO", IF(B46="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G46" s="11">
+        <f>IF(C46="SI", "🟢 Aprobada", IF(B46="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Inteligencia artifical</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E47" s="10">
+        <f>IF(B47="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F47" s="10">
+        <f>IF(C47="SI", "APROBADO", IF(B47="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G47" s="11">
+        <f>IF(C47="SI", "🟢 Aprobada", IF(B47="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Lengua extranjera</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E48" s="10">
+        <f>IF(B48="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F48" s="10">
+        <f>IF(C48="SI", "APROBADO", IF(B48="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G48" s="11">
+        <f>IF(C48="SI", "🟢 Aprobada", IF(B48="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>Sistema y politica educativa</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E49" s="10">
+        <f>IF(B49="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F49" s="10">
+        <f>IF(C49="SI", "APROBADO", IF(B49="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G49" s="11">
+        <f>IF(C49="SI", "🟢 Aprobada", IF(B49="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A44:G44"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A31:G31"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="I10:J10"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A35:G35"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="I14:J14"/>
@@ -1893,7 +2131,7 @@
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B14 B15 B16 B17 B18 B19 B20 B21 B23 B24 B25 B26 B27 B28 B29 B30 B32 B33 B34 B35 B36 B37 B38 B40 B41 B42 C6 C7 C8 C9 C10 C11 C12 C14 C15 C16 C17 C18 C19 C20 C21 C23 C24 C25 C26 C27 C28 C29 C30 C32 C33 C34 C35 C36 C37 C38 C40 C41 C42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B17 B18 B19 B20 B21 B22 B23 B24 B25 B27 B28 B29 B30 B31 B32 B33 B34 B36 B37 B38 B39 B40 B41 B42 B43 B45 B46 B47 B48 B49 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C17 C18 C19 C20 C21 C22 C23 C24 C25 C27 C28 C29 C30 C31 C32 C33 C34 C36 C37 C38 C39 C40 C41 C42 C43 C45 C46 C47 C48 C49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>
